--- a/DOSSIES_MULTIFORMATO/SEPROR/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SEPROR/dossie.xlsx
@@ -636,7 +636,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2016NE01079</t>
+          <t>2016NE01074</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1475.29</v>
+        <v>3118.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -655,14 +655,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DO EMPENHO N° 913/2016, DEVIDO ENCERRAMENTO DO EXERCÍCIO FINANCEIRO, CONFORME ORIENTAÇÃO DO ÓRGÃO CENTRALIZADOR (SEFAZ).</t>
+          <t>CANCELAMENTO DE SALDO DO EMPENHO N° 064/2016, DEVIDO ENCERRAMENTO DO EXERCÍCIO FINANCEIRO, CONFORME ORIENTAÇÃO DO ÓRGÃO CENTRALIZADOR (SEFAZ).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2016NE01078</t>
+          <t>2016NE01075</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4349.48</v>
+        <v>901.96</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DO EMPENHO N° 911/2016, DEVIDO ENCERRAMENTO DO EXERCÍCIO FINANCEIRO, CONFORME ORIENTAÇÃO DO ÓRGÃO CENTRALIZADOR (SEFAZ).</t>
+          <t>CANCELAMENTO DE SALDO DO EMPENHO N° 338/2016, DEVIDO ENCERRAMENTO DO EXERCÍCIO FINANCEIRO, CONFORME ORIENTAÇÃO DO ÓRGÃO CENTRALIZADOR (SEFAZ).</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2016NE01075</t>
+          <t>2016NE01078</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>901.96</v>
+        <v>4349.48</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -733,14 +733,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DO EMPENHO N° 338/2016, DEVIDO ENCERRAMENTO DO EXERCÍCIO FINANCEIRO, CONFORME ORIENTAÇÃO DO ÓRGÃO CENTRALIZADOR (SEFAZ).</t>
+          <t>CANCELAMENTO DE SALDO DO EMPENHO N° 911/2016, DEVIDO ENCERRAMENTO DO EXERCÍCIO FINANCEIRO, CONFORME ORIENTAÇÃO DO ÓRGÃO CENTRALIZADOR (SEFAZ).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2016NE01074</t>
+          <t>2016NE01079</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3118.8</v>
+        <v>1475.29</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -759,19 +759,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DO EMPENHO N° 064/2016, DEVIDO ENCERRAMENTO DO EXERCÍCIO FINANCEIRO, CONFORME ORIENTAÇÃO DO ÓRGÃO CENTRALIZADOR (SEFAZ).</t>
+          <t>CANCELAMENTO DE SALDO DO EMPENHO N° 913/2016, DEVIDO ENCERRAMENTO DO EXERCÍCIO FINANCEIRO, CONFORME ORIENTAÇÃO DO ÓRGÃO CENTRALIZADOR (SEFAZ).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2017NE01041</t>
+          <t>2017NE01038</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12/2016</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3070.24</v>
+        <v>1554.66</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -789,19 +789,19 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PRORROGAÇÃO DO PRAZO DE VIGÊNCIA POR MAIS 12 MESES E REAJUSTE DE 3,36% NO SERVIÇO DE CESSÃO DE LICENÇA DE USO DO SISTEMA SGTI- CHAMADAS, FERRAMENTA PARA DAR SUPORTE À GESTÃO DE DEMANDAS EXTERNAS E INT</t>
+          <t xml:space="preserve">Reforço da NE n° 398/2017 referente ao 1° Termo Aditivo ao Contrato n° 11/2016-SEPROR, com vigência de 23/05/2017 até 22/05/2018, cujo objeto é Contratação de Empresa especializada em desenvolvimento </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2017NE01039</t>
+          <t>2017NE01042</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6/2017</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1642.29</v>
+        <v>17640</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -819,19 +819,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na construção de circuito de fibra óptica para instalar link de acesso a rede mundial e fornecimento de acesso a rede METROMAO.</t>
+          <t>Prorrogação por mais 12 meses e supressão de 2% do contrato inicial.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2017NE01042</t>
+          <t>2017NE01039</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>6/2017</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17640</v>
+        <v>1642.29</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -849,19 +849,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Prorrogação por mais 12 meses e supressão de 2% do contrato inicial.</t>
+          <t>Contratação de empresa especializada na construção de circuito de fibra óptica para instalar link de acesso a rede mundial e fornecimento de acesso a rede METROMAO.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2017NE01038</t>
+          <t>2017NE01041</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>12/2016</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1554.66</v>
+        <v>3070.24</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforço da NE n° 398/2017 referente ao 1° Termo Aditivo ao Contrato n° 11/2016-SEPROR, com vigência de 23/05/2017 até 22/05/2018, cujo objeto é Contratação de Empresa especializada em desenvolvimento </t>
+          <t>PRORROGAÇÃO DO PRAZO DE VIGÊNCIA POR MAIS 12 MESES E REAJUSTE DE 3,36% NO SERVIÇO DE CESSÃO DE LICENÇA DE USO DO SISTEMA SGTI- CHAMADAS, FERRAMENTA PARA DAR SUPORTE À GESTÃO DE DEMANDAS EXTERNAS E INT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025NE0000902</t>
+          <t>2025NE0000900</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4/2022</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6327.94</v>
+        <v>5026.28</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -909,19 +909,19 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025NE0000899</t>
+          <t>2025NE0000901</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19500</v>
+        <v>2579.92</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -939,19 +939,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 06.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de Sistema de Protocolo via Web - (SPROWEB). TC: 0002/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025NE0000901</t>
+          <t>2025NE0000899</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2579.92</v>
+        <v>19500</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -969,19 +969,19 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de Sistema de Protocolo via Web - (SPROWEB). TC: 0002/2024 AD: 01.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 06.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025NE0000900</t>
+          <t>2025NE0000902</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5026.28</v>
+        <v>6327.94</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -999,19 +999,19 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 04.</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023NE0001602</t>
+          <t>2023NE0001603</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>3/2019</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12064.5</v>
+        <v>1189.56</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1029,19 +1029,19 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 004/2021 AD: 02.</t>
+          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB). TC: 0003/2019 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023NE0001600</t>
+          <t>2023NE0001601</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2317.54</v>
+        <v>2916.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1059,19 +1059,19 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 006/2021 AD: 02.</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023NE0001601</t>
+          <t>2023NE0001600</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4/2022</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2916.1</v>
+        <v>2317.54</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1089,19 +1089,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 006/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023NE0001603</t>
+          <t>2023NE0001602</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3/2019</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1189.56</v>
+        <v>12064.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1119,19 +1119,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB). TC: 0003/2019 AD: 04.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 004/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025NE0000788</t>
+          <t>2025NE0000789</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2513.14</v>
+        <v>3163.97</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1149,19 +1149,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 04.</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025NE0000785</t>
+          <t>2025NE0000787</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>9750</v>
+        <v>1289.96</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1179,19 +1179,19 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 06.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de Sistema de Protocolo via Web - (SPROWEB). TC: 0002/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025NE0000787</t>
+          <t>2025NE0000785</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1289.96</v>
+        <v>9750</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1209,19 +1209,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de Sistema de Protocolo via Web - (SPROWEB). TC: 0002/2024 AD: 01.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 06.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025NE0000789</t>
+          <t>2025NE0000788</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4/2022</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3163.97</v>
+        <v>2513.14</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 04.</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2015NE00756</t>
+          <t>2015NE00754</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1295,14 +1295,14 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ERRO NA DESCRIÇÃO</t>
+          <t>serviço de processamento de dados, para uso de programa de computação , para disponibilização do sistema de protocolo em plataforma web (sproweb).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2015NE00754</t>
+          <t>2015NE00756</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1325,14 +1325,14 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>serviço de processamento de dados, para uso de programa de computação , para disponibilização do sistema de protocolo em plataforma web (sproweb).</t>
+          <t>ERRO NA DESCRIÇÃO</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2018NE00902</t>
+          <t>2018NE00904</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14199.1</v>
+        <v>3070.24</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1351,14 +1351,14 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE N° 166, PARA AJUSTE ORÇAMENTÁRIO E EM CUMPRIMENTO AO ART. 42 DA LRF.</t>
+          <t>ANULAÇÃO DA NE N° 164, PARA AJUSTE ORÇAMENTÁRIO E EM CUMPRIMENTO AO ART. 42 DA LRF.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2018NE00903</t>
+          <t>2018NE00917</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>17052</v>
+        <v>1919.82</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1377,14 +1377,14 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE N° 163, PARA AJUSTE ORÇAMENTÁRIO E EM CUMPRIMENTO AO ART. 42 DA LRF.</t>
+          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2018NE00901</t>
+          <t>2018NE00916</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>414.58</v>
+        <v>1554.7</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1403,14 +1403,14 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE N° 167, PARA AJUSTE ORÇAMENTÁRIO E EM CUMPRIMENTO AO ART. 42 DA LRF.</t>
+          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2018NE00916</t>
+          <t>2018NE00901</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1554.7</v>
+        <v>414.58</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1429,14 +1429,14 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
+          <t>ANULAÇÃO DA NE N° 167, PARA AJUSTE ORÇAMENTÁRIO E EM CUMPRIMENTO AO ART. 42 DA LRF.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2018NE00917</t>
+          <t>2018NE00903</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1919.82</v>
+        <v>17052</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1455,14 +1455,14 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
+          <t>ANULAÇÃO DA NE N° 163, PARA AJUSTE ORÇAMENTÁRIO E EM CUMPRIMENTO AO ART. 42 DA LRF.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2018NE00904</t>
+          <t>2018NE00902</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3070.24</v>
+        <v>14199.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1481,14 +1481,14 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE N° 164, PARA AJUSTE ORÇAMENTÁRIO E EM CUMPRIMENTO AO ART. 42 DA LRF.</t>
+          <t>ANULAÇÃO DA NE N° 166, PARA AJUSTE ORÇAMENTÁRIO E EM CUMPRIMENTO AO ART. 42 DA LRF.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2024NE0001356</t>
+          <t>2024NE0001351</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.01</v>
+        <v>356.87</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DE EMPENHO N° 494/2024, EM CUMPRIMENTO AO DECRETO N° 50.522 DE 22 DE OUTUBRO DE 2024.</t>
+          <t>CANCELAMENTO DO SALDO DE EMPENHO N° 623/2024, EM CUMPRIMENTO AO DECRETO N° 50.522 DE 22 DE OUTUBRO DE 2024.</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2024NE0001351</t>
+          <t>2024NE0001356</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>356.87</v>
+        <v>0.01</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DO SALDO DE EMPENHO N° 623/2024, EM CUMPRIMENTO AO DECRETO N° 50.522 DE 22 DE OUTUBRO DE 2024.</t>
+          <t>ANULAÇÃO DO SALDO DE EMPENHO N° 494/2024, EM CUMPRIMENTO AO DECRETO N° 50.522 DE 22 DE OUTUBRO DE 2024.</t>
         </is>
       </c>
     </row>
@@ -1592,10 +1592,14 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2024NE0000934</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>2024NE0000935</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>4/2022</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr">
         <is>
           <t>27/08/2024</t>
@@ -1611,21 +1615,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>anulação de saldo da Nota de Empenho, em virtude de que o término do contrato ocorreu em 24/07/2024, totalizando o valor de R$ 2.338,88, ou seja, foi empenhado a maior.</t>
+          <t>Reforço da 2024NE00779, referente a complementação do valor do mês de julho/2024, correspondente ao Termo Contrato Nº 004/2022 Aditivo nº 02</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2024NE0000935</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>4/2022</t>
-        </is>
-      </c>
+          <t>2024NE0000934</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>27/08/2024</t>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Reforço da 2024NE00779, referente a complementação do valor do mês de julho/2024, correspondente ao Termo Contrato Nº 004/2022 Aditivo nº 02</t>
+          <t>anulação de saldo da Nota de Empenho, em virtude de que o término do contrato ocorreu em 24/07/2024, totalizando o valor de R$ 2.338,88, ou seja, foi empenhado a maior.</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1678,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025NE0000642</t>
+          <t>2025NE0000640</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4/2022</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3163.97</v>
+        <v>2513.14</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1701,19 +1701,19 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025NE0000641</t>
+          <t>2025NE0000639</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1722,7 +1722,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1289.96</v>
+        <v>9750</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1731,19 +1731,19 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de Sistema de Protocolo via Web - (SPROWEB). TC: 0002/2024 AD: 01.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 06.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025NE0000639</t>
+          <t>2025NE0000641</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>9750</v>
+        <v>1289.96</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1761,19 +1761,19 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 06.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de Sistema de Protocolo via Web - (SPROWEB). TC: 0002/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025NE0000640</t>
+          <t>2025NE0000642</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2513.14</v>
+        <v>3163.97</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1791,14 +1791,14 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 04.</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2019NE00544</t>
+          <t>2019NE00546</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1854,7 +1854,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2019NE00546</t>
+          <t>2019NE00544</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1884,12 +1884,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2017NE00575</t>
+          <t>2017NE00570</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2/2012</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1559.4</v>
+        <v>18000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1907,14 +1907,14 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Para atender Despesas de Exercícios Anteriores com Serviços de Processamentos de Dados - Especializado em Sessão de Uso de Programa de Protocolo (SPROWEB), referente ao mês de Novembro/2015.</t>
+          <t>Para atender Despesas de Exercícios Anteriores com Serviços de Despesas de Teleprocessamento - (Serviços de Acesso à Internet), NFS-e n° 20949 de 01/12/2016 referente ao mês de Dezembro/2016.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2017NE00574</t>
+          <t>2017NE00572</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1937,14 +1937,14 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Para atender Despesas de Exercícios Anteriores com Serviços de Processamentos de Dados - Especializado em Sessão de Uso de Programa de Protocolo (SPROWEB), referente ao mês de Outubro/2015.</t>
+          <t>Para atender Despesas de Exercícios Anteriores com Serviços de Processamentos de Dados - Especializado em Sessão de Uso de Programa de Protocolo (SPROWEB), referente ao mês de Dezembro/2015.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2017NE00572</t>
+          <t>2017NE00574</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1967,19 +1967,19 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Para atender Despesas de Exercícios Anteriores com Serviços de Processamentos de Dados - Especializado em Sessão de Uso de Programa de Protocolo (SPROWEB), referente ao mês de Dezembro/2015.</t>
+          <t>Para atender Despesas de Exercícios Anteriores com Serviços de Processamentos de Dados - Especializado em Sessão de Uso de Programa de Protocolo (SPROWEB), referente ao mês de Outubro/2015.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2017NE00570</t>
+          <t>2017NE00575</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>2/2012</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>18000</v>
+        <v>1559.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Para atender Despesas de Exercícios Anteriores com Serviços de Despesas de Teleprocessamento - (Serviços de Acesso à Internet), NFS-e n° 20949 de 01/12/2016 referente ao mês de Dezembro/2016.</t>
+          <t>Para atender Despesas de Exercícios Anteriores com Serviços de Processamentos de Dados - Especializado em Sessão de Uso de Programa de Protocolo (SPROWEB), referente ao mês de Novembro/2015.</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2023NE01272</t>
+          <t>2023NE0001272</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2087,14 +2087,14 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1º Termo Aditivo ao Contrato 004/2022.</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2023NE0001272</t>
+          <t>2023NE01272</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>1º Termo Aditivo ao Contrato 004/2022.</t>
         </is>
       </c>
     </row>
@@ -2184,12 +2184,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025NE0000123</t>
+          <t>2025NE0000122</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4635.08</v>
+        <v>2379.12</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2207,19 +2207,19 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 03.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de Sistema de Protocolo via Web - (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025NE0000122</t>
+          <t>2025NE0000123</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2379.12</v>
+        <v>4635.08</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de Sistema de Protocolo via Web - (SPROWEB).</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 03.</t>
         </is>
       </c>
     </row>
@@ -2330,12 +2330,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025NE0000449</t>
+          <t>2025NE0000451</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>19500</v>
+        <v>5026.28</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2353,19 +2353,19 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 06.</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025NE0000450</t>
+          <t>2025NE0000452</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>4/2022</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2430.08</v>
+        <v>2579.92</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2383,19 +2383,19 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de Sistema de Protocolo via Web - (SPROWEB). TC: 0002/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025NE0000452</t>
+          <t>2025NE0000450</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2579.92</v>
+        <v>2430.08</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2413,19 +2413,19 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de Sistema de Protocolo via Web - (SPROWEB). TC: 0002/2024 AD: 01.</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025NE0000451</t>
+          <t>2025NE0000449</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5026.28</v>
+        <v>19500</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 04.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 06.</t>
         </is>
       </c>
     </row>
@@ -2480,12 +2480,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025NE0000119</t>
+          <t>2025NE0000121</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2494,7 +2494,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>15382.25</v>
+        <v>5832.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2503,19 +2503,19 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 05.</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025NE0000121</t>
+          <t>2025NE0000119</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>4/2022</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>5832.2</v>
+        <v>15382.25</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2533,19 +2533,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 05.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2022NE0002315</t>
+          <t>2022NE0002314</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>3/2019</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2554,7 +2554,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2232.91</v>
+        <v>1167.84</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2563,19 +2563,19 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web)</t>
+          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2022NE0002314</t>
+          <t>2022NE0002315</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>3/2019</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1167.84</v>
+        <v>2232.91</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2593,19 +2593,19 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB).</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2024NE0001122</t>
+          <t>2024NE0001126</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>9048.379999999999</v>
+        <v>1189.56</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2623,19 +2623,19 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 05.</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web).</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2024NE0001124</t>
+          <t>2024NE0001121</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2317.54</v>
+        <v>2916.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2653,19 +2653,19 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 03.</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2024NE0001121</t>
+          <t>2024NE0001124</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>4/2022</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2916.1</v>
+        <v>2317.54</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2683,19 +2683,19 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2024NE0001126</t>
+          <t>2024NE0001122</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1189.56</v>
+        <v>9048.379999999999</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2713,19 +2713,19 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web).</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 05.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2022NE0001745</t>
+          <t>2022NE0001746</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>3/2019</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>4465.82</v>
+        <v>2335.68</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web)</t>
+          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB).</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2022NE0001746</t>
+          <t>2022NE0001745</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>3/2019</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2335.68</v>
+        <v>4465.82</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB).</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web)</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2017NE01132</t>
+          <t>2017NE01123</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>58.2</v>
+        <v>3070.24</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3005,14 +3005,14 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DE EMPENHO N° 00398, EM ATENDIMENTO A INSTRUÇÃO NORMATIVA N° 0001/2017 - GSEFAZ DE 12/12/2017.</t>
+          <t>ANULAÇÃO DO SALDO DE EMPENHO N° 00458, EM ATENDIMENTO A INSTRUÇÃO NORMATIVA N.0001/2017 - GSEFAZ DE 12/12/2017.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2017NE01120</t>
+          <t>2017NE01112</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>8580</v>
+        <v>2625.72</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3031,14 +3031,14 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DE EMPENHO N° 00219, EM ATENDIMENTO A INSTRUÇÃO NORMATIVA N.0001/2017 - GSEFAZ DE 12/12/2017. OBS.: ANULAÇÃO PARCIAL EM VIRTUDE QUE CONSTA PENDENTE A FATURA DO MÊS DE AGOSTO/2017.</t>
+          <t>CANCELAMENTO EM ATENDIMENTO A INSTRUÇÃO NORMATIVA N.0001/2017 - GSEFAZ DE 12/12/2017.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2017NE01126</t>
+          <t>2017NE01121</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1642.29</v>
+        <v>2970.43</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DE EMPENHO N° 00553, EM ATENDIMENTO A INSTRUÇÃO NORMATIVA N.0001/2017 - GSEFAZ DE 12/12/2017.</t>
+          <t>ANULAÇÃO DO SALDO DE EMPENHO N° 00297, EM ATENDIMENTO A INSTRUÇÃO NORMATIVA N.0001/2017 - GSEFAZ DE 12/12/2017.</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2017NE01121</t>
+          <t>2017NE01126</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2970.43</v>
+        <v>1642.29</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3109,14 +3109,14 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DE EMPENHO N° 00297, EM ATENDIMENTO A INSTRUÇÃO NORMATIVA N.0001/2017 - GSEFAZ DE 12/12/2017.</t>
+          <t>ANULAÇÃO DO SALDO DE EMPENHO N° 00553, EM ATENDIMENTO A INSTRUÇÃO NORMATIVA N.0001/2017 - GSEFAZ DE 12/12/2017.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2017NE01112</t>
+          <t>2017NE01120</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2625.72</v>
+        <v>8580</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3135,14 +3135,14 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CANCELAMENTO EM ATENDIMENTO A INSTRUÇÃO NORMATIVA N.0001/2017 - GSEFAZ DE 12/12/2017.</t>
+          <t>ANULAÇÃO DO SALDO DE EMPENHO N° 00219, EM ATENDIMENTO A INSTRUÇÃO NORMATIVA N.0001/2017 - GSEFAZ DE 12/12/2017. OBS.: ANULAÇÃO PARCIAL EM VIRTUDE QUE CONSTA PENDENTE A FATURA DO MÊS DE AGOSTO/2017.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2017NE01123</t>
+          <t>2017NE01132</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>3070.24</v>
+        <v>58.2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3161,19 +3161,19 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DE EMPENHO N° 00458, EM ATENDIMENTO A INSTRUÇÃO NORMATIVA N.0001/2017 - GSEFAZ DE 12/12/2017.</t>
+          <t>ANULAÇÃO DO SALDO DE EMPENHO N° 00398, EM ATENDIMENTO A INSTRUÇÃO NORMATIVA N° 0001/2017 - GSEFAZ DE 12/12/2017.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2024NE0000872</t>
+          <t>2024NE0000869</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2317.54</v>
+        <v>9048.379999999999</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3191,19 +3191,19 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 03.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 05.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2024NE0000871</t>
+          <t>2024NE0000870</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>4/2022</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2916.1</v>
+        <v>1189.56</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3221,19 +3221,19 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2024NE0000870</t>
+          <t>2024NE0000871</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1189.56</v>
+        <v>2916.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3251,19 +3251,19 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web).</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2024NE0000869</t>
+          <t>2024NE0000872</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3272,7 +3272,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>9048.379999999999</v>
+        <v>2317.54</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 05.</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 03.</t>
         </is>
       </c>
     </row>
@@ -3438,12 +3438,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2024NE0000077</t>
+          <t>2024NE0000079</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3/2019</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2379.12</v>
+        <v>5832.2</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB). TC: 0003/2019 AD: 04.</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
@@ -3498,12 +3498,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2024NE0000079</t>
+          <t>2024NE0000077</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>4/2022</t>
+          <t>3/2019</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>5832.2</v>
+        <v>2379.12</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3521,19 +3521,19 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB). TC: 0003/2019 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2024NE0001010</t>
+          <t>2024NE0001009</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>9048.379999999999</v>
+        <v>1189.56</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3551,19 +3551,19 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 05.</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web).</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2024NE0001007</t>
+          <t>2024NE0001008</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2317.54</v>
+        <v>2916.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3581,19 +3581,19 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 03.</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2024NE0001008</t>
+          <t>2024NE0001007</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>4/2022</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2916.1</v>
+        <v>2317.54</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3611,19 +3611,19 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2024NE0001009</t>
+          <t>2024NE0001010</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1189.56</v>
+        <v>9048.379999999999</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web).</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 05.</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2015NE01995</t>
+          <t>2015NE01982</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>14034.6</v>
+        <v>3000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2015NE01982</t>
+          <t>2015NE01995</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -3770,7 +3770,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>3000</v>
+        <v>14034.6</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2022NE0000853</t>
+          <t>2022NE0000854</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -3826,7 +3826,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>817.14</v>
+        <v>820.1799999999999</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3835,14 +3835,14 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>REFERENTE À EXECUÇÃO DE FOLHA DE PAGAMENTO ESPECIAL – TIPO 68 DO MÊS: SETEMBRO/2021, CONFORME NFSe Nº 25079 DE 27/10/2021, PARECER JURÍDICO Nº 121/2022—ASJUR/SEPROR DE 30/03/2022.</t>
+          <t>REFERENTE À EXECUÇÃO DE FOLHA DE PAGAMENTO ESPECIAL – TIPO 68 DO MÊS: JULHO/2021, CONFORME NFSe Nº 24913 DE 26/10/2021, PARECER JURÍDICO Nº 118/2022—ASJUR/SEPROR DE 23/03/2022.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2022NE0000854</t>
+          <t>2022NE0000853</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>820.1799999999999</v>
+        <v>817.14</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>REFERENTE À EXECUÇÃO DE FOLHA DE PAGAMENTO ESPECIAL – TIPO 68 DO MÊS: JULHO/2021, CONFORME NFSe Nº 24913 DE 26/10/2021, PARECER JURÍDICO Nº 118/2022—ASJUR/SEPROR DE 23/03/2022.</t>
+          <t>REFERENTE À EXECUÇÃO DE FOLHA DE PAGAMENTO ESPECIAL – TIPO 68 DO MÊS: SETEMBRO/2021, CONFORME NFSe Nº 25079 DE 27/10/2021, PARECER JURÍDICO Nº 121/2022—ASJUR/SEPROR DE 30/03/2022.</t>
         </is>
       </c>
     </row>
@@ -3928,12 +3928,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2024NE0000231</t>
+          <t>2024NE0000236</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>4/2022</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3942,7 +3942,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>5832.2</v>
+        <v>4017.08</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3951,19 +3951,19 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2024NE0000233</t>
+          <t>2024NE0000232</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>3/2019</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>15382.25</v>
+        <v>2379.12</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3981,19 +3981,19 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 04.</t>
+          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB). TC: 0003/2019 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2024NE0000232</t>
+          <t>2024NE0000233</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3/2019</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2379.12</v>
+        <v>15382.25</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4011,19 +4011,19 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB). TC: 0003/2019 AD: 04.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2024NE0000236</t>
+          <t>2024NE0000231</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>4017.08</v>
+        <v>5832.2</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 02.</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
@@ -4108,12 +4108,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2024NE0000226</t>
+          <t>2024NE0000227</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>4/2022</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4122,7 +4122,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2916.1</v>
+        <v>9048.379999999999</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Para atender despesas de Exercícios Anteriores com prestação de Serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO, referente ao 1º Termo Aditivo ao Contrato nº 04/2022-SEPR</t>
+          <t>Para atender despesas de Exercícios Anteriores com prestação de Serviços de acesso gerenciado a Rede Mundial, referente ao 3º Termo Aditivo ao Contrato nº 04/2021-SEPROR/PRODAM S.A – conforme Fatura n</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2024NE0000227</t>
+          <t>2024NE0000226</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>9048.379999999999</v>
+        <v>2916.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Para atender despesas de Exercícios Anteriores com prestação de Serviços de acesso gerenciado a Rede Mundial, referente ao 3º Termo Aditivo ao Contrato nº 04/2021-SEPROR/PRODAM S.A – conforme Fatura n</t>
+          <t>Para atender despesas de Exercícios Anteriores com prestação de Serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO, referente ao 1º Termo Aditivo ao Contrato nº 04/2022-SEPR</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2023NE00907</t>
+          <t>2023NE0000907</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4311,14 +4311,14 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Cobertura Financeira</t>
+          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB). TC: 0003/2019 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2023NE0000907</t>
+          <t>2023NE00907</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB). TC: 0003/2019 AD: 04.</t>
+          <t>Cobertura Financeira</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2023NE0001460</t>
+          <t>2023NE0001462</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>3/2019</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>12064.5</v>
+        <v>1189.56</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 004/2021 AD: 02.</t>
+          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB). TC: 0003/2019 AD: 04.</t>
         </is>
       </c>
     </row>
@@ -4438,12 +4438,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2023NE0001462</t>
+          <t>2023NE0001460</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>3/2019</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1189.56</v>
+        <v>12064.5</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB). TC: 0003/2019 AD: 04.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 004/2021 AD: 02.</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2016NE00338</t>
+          <t>2016NE00336</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4734,7 +4734,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2016NE00336</t>
+          <t>2016NE00338</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4794,12 +4794,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2024NE0001272</t>
+          <t>2024NE0001270</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>4/2022</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4808,7 +4808,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>2916.1</v>
+        <v>9048.379999999999</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -4817,14 +4817,14 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 05.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2024NE0001271</t>
+          <t>2024NE0001273</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1189.56</v>
+        <v>2317.54</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -4847,14 +4847,14 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web).</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2024NE0001273</t>
+          <t>2024NE0001271</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4868,7 +4868,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2317.54</v>
+        <v>1189.56</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -4877,19 +4877,19 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 03.</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web).</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2024NE0001270</t>
+          <t>2024NE0001272</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4898,7 +4898,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>9048.379999999999</v>
+        <v>2916.1</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4907,14 +4907,14 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 05.</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2023NE0001617</t>
+          <t>2023NE0001618</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1189.56</v>
+        <v>2317.54</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB). TC: 0003/2019 AD: 04.</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 006/2021 AD: 02.</t>
         </is>
       </c>
     </row>
@@ -4974,7 +4974,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2023NE0001618</t>
+          <t>2023NE0001617</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>2317.54</v>
+        <v>1189.56</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 006/2021 AD: 02.</t>
+          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB). TC: 0003/2019 AD: 04.</t>
         </is>
       </c>
     </row>
@@ -5030,12 +5030,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2024NE0000494</t>
+          <t>2024NE0000498</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>3/2019</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5044,7 +5044,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1699.54</v>
+        <v>1268.86</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5053,19 +5053,19 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 02.</t>
+          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB). TC: 0003/2019 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2024NE0000499</t>
+          <t>2024NE0000495</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>4/2022</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>5832.2</v>
+        <v>18096.76</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5083,19 +5083,19 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 05.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2024NE0000495</t>
+          <t>2024NE0000499</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>18096.76</v>
+        <v>5832.2</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5113,19 +5113,19 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 05.</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2024NE0000498</t>
+          <t>2024NE0000494</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>3/2019</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1268.86</v>
+        <v>1699.54</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5143,19 +5143,19 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB). TC: 0003/2019 AD: 04.</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2018NE00167</t>
+          <t>2018NE00163</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>7773.3</v>
+        <v>52920</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5173,24 +5173,28 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>PRORROGAÇÃO DE PRAZO DO CONTRATO PRIMITIVO POR MAIS 12 MESES, COM REAJUSTE CONTRATUAL DE 5,38%, NA LICENÇA DE USO DO SISTEMA DE INFORMAÇÃO- GERWEB.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET, COM A PRORROGAÇÃO DE PRAZO E SUPRESSÃO DE 2% DO CONTRTO INICIAL.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2018NE00162</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr"/>
+          <t>2018NE00166</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>12/2017</t>
+        </is>
+      </c>
       <c r="C158" t="inlineStr">
         <is>
           <t>07/02/2018</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>52920</v>
+        <v>37224.99</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5199,24 +5203,28 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>NULAÇÃO, CONFORME SOLICITAÇÃO DA ORIENTAÇÃO TÉCNICA Nº 12/2018-GINS/SEFAZ DE 07/02/2018. VISANDO ALTERAÇÃO NO PLANO DE CONTAS DO SISTEMA AFI.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA A PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2018NE00159</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr"/>
+          <t>2018NE00164</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>12/2016</t>
+        </is>
+      </c>
       <c r="C159" t="inlineStr">
         <is>
           <t>07/02/2018</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>7773.3</v>
+        <v>18421.44</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5225,14 +5233,14 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>ANULAÇÃO CONFORME SOLICITADO, ATRAVÉS DA ORIENTAÇÃO TÉCNICA Nº 12/2018-GINS/SEFAZ DE 07/02/2018.</t>
+          <t>PRORROGAÇÃO DO PRAZO DE VIGÊNCIA POR MAIS 12 MESES E REAJUSTE DE 3,36% NO SERVIÇO DE CESSÃO DE LICENÇA DE USO DO SISTEMA SGTI- CHAMADAS, FERRAMENTA PARA DAR SUPORTE À GESTÃO DE DEMANDAS EXTERNAS E INT</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2018NE00161</t>
+          <t>2018NE00160</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
@@ -5242,7 +5250,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>11496.03</v>
+        <v>37224.99</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5251,28 +5259,24 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>ANULAÇÃO, CONFORME SOLICITAÇÃO DA ORIENTAÇÃO TÉCNICA Nº 12/2018-GINS/SEFAZ DE 07/02/2018.</t>
+          <t>CANCELAMENTO DA NE00064 DE 02/01/2018, CONFORME ORIENTAÇÃO TÉCNICA N° 12 - GINS/SEFAZ DE 07/02/2018.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2018NE00165</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>6/2017</t>
-        </is>
-      </c>
+          <t>2018NE00158</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
           <t>07/02/2018</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>11496.03</v>
+        <v>18421.44</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5281,24 +5285,28 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA CONSTRUÇÃO DE CIRCUITO OPTICA PARA INSTALAR LINK DE ACESSO A REDE MUNDIAL E FORNECIMENTO DE ACESSO A REDE METROMAO.</t>
+          <t>CANCELAMENTO DA NE00063 DE 02/01/2018, CONFORME ORIENTAÇÃO TÉCNICA N° 12 - GINS/SEFAZ DE 07/02/2018.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2018NE00158</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr"/>
+          <t>2018NE00165</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>6/2017</t>
+        </is>
+      </c>
       <c r="C162" t="inlineStr">
         <is>
           <t>07/02/2018</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>18421.44</v>
+        <v>11496.03</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5307,14 +5315,14 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DA NE00063 DE 02/01/2018, CONFORME ORIENTAÇÃO TÉCNICA N° 12 - GINS/SEFAZ DE 07/02/2018.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA CONSTRUÇÃO DE CIRCUITO OPTICA PARA INSTALAR LINK DE ACESSO A REDE MUNDIAL E FORNECIMENTO DE ACESSO A REDE METROMAO.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2018NE00160</t>
+          <t>2018NE00161</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
@@ -5324,7 +5332,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>37224.99</v>
+        <v>11496.03</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5333,28 +5341,24 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DA NE00064 DE 02/01/2018, CONFORME ORIENTAÇÃO TÉCNICA N° 12 - GINS/SEFAZ DE 07/02/2018.</t>
+          <t>ANULAÇÃO, CONFORME SOLICITAÇÃO DA ORIENTAÇÃO TÉCNICA Nº 12/2018-GINS/SEFAZ DE 07/02/2018.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2018NE00164</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>12/2016</t>
-        </is>
-      </c>
+          <t>2018NE00159</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
           <t>07/02/2018</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>18421.44</v>
+        <v>7773.3</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5363,28 +5367,24 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>PRORROGAÇÃO DO PRAZO DE VIGÊNCIA POR MAIS 12 MESES E REAJUSTE DE 3,36% NO SERVIÇO DE CESSÃO DE LICENÇA DE USO DO SISTEMA SGTI- CHAMADAS, FERRAMENTA PARA DAR SUPORTE À GESTÃO DE DEMANDAS EXTERNAS E INT</t>
+          <t>ANULAÇÃO CONFORME SOLICITADO, ATRAVÉS DA ORIENTAÇÃO TÉCNICA Nº 12/2018-GINS/SEFAZ DE 07/02/2018.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2018NE00166</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>12/2017</t>
-        </is>
-      </c>
+          <t>2018NE00162</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
           <t>07/02/2018</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>37224.99</v>
+        <v>52920</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5393,19 +5393,19 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA A PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO.</t>
+          <t>NULAÇÃO, CONFORME SOLICITAÇÃO DA ORIENTAÇÃO TÉCNICA Nº 12/2018-GINS/SEFAZ DE 07/02/2018. VISANDO ALTERAÇÃO NO PLANO DE CONTAS DO SISTEMA AFI.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2018NE00163</t>
+          <t>2018NE00167</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5414,7 +5414,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>52920</v>
+        <v>7773.3</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE ACESSO A INTERNET, COM A PRORROGAÇÃO DE PRAZO E SUPRESSÃO DE 2% DO CONTRTO INICIAL.</t>
+          <t>PRORROGAÇÃO DE PRAZO DO CONTRATO PRIMITIVO POR MAIS 12 MESES, COM REAJUSTE CONTRATUAL DE 5,38%, NA LICENÇA DE USO DO SISTEMA DE INFORMAÇÃO- GERWEB.</t>
         </is>
       </c>
     </row>
@@ -5490,12 +5490,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2023NE0001054</t>
+          <t>2023NE0001055</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>3/2019</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>24129</v>
+        <v>2379.12</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5513,19 +5513,19 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 004/2021 AD: 02.</t>
+          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB). TC: 0003/2019 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2023NE0001053</t>
+          <t>2023NE0001056</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5534,7 +5534,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>4635.08</v>
+        <v>2329.02</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5543,19 +5543,19 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 006/2021 AD: 02.</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2023NE0001056</t>
+          <t>2023NE0001053</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>4/2022</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5564,7 +5564,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>2329.02</v>
+        <v>4635.08</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5573,19 +5573,19 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 006/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2023NE0001055</t>
+          <t>2023NE0001054</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>3/2019</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>2379.12</v>
+        <v>24129</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB). TC: 0003/2019 AD: 04.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 004/2021 AD: 02.</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2025NE0000302</t>
+          <t>2025NE0000301</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>4/2022</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>5832.2</v>
+        <v>1268.86</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -5663,19 +5663,19 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de Sistema de Protocolo via Web - (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2025NE0000300</t>
+          <t>2025NE0000299</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5684,7 +5684,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1699.44</v>
+        <v>19500</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 03.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 06.</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2025NE0000299</t>
+          <t>2025NE0000300</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>19500</v>
+        <v>1699.44</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -5753,19 +5753,19 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 06.</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2025NE0000301</t>
+          <t>2025NE0000302</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5774,7 +5774,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1268.86</v>
+        <v>5832.2</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5783,14 +5783,14 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de Sistema de Protocolo via Web - (SPROWEB).</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2015NE00294</t>
+          <t>2015NE00291</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>PGTO DE SERVIÇO DE CESSÃO DE USO DO SISTEMA SPROWEB, EXERCICIOS ANTERIORES</t>
+          <t>PGTO DE SERVIÇO DE CESSÃO DO SISTEMA SPROWEB EXERCICIOS ANTERIORES</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2015NE00291</t>
+          <t>2015NE00294</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5873,19 +5873,19 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>PGTO DE SERVIÇO DE CESSÃO DO SISTEMA SPROWEB EXERCICIOS ANTERIORES</t>
+          <t>PGTO DE SERVIÇO DE CESSÃO DE USO DO SISTEMA SPROWEB, EXERCICIOS ANTERIORES</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2019NE00466</t>
+          <t>2019NE00465</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>6/2017</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5894,7 +5894,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1316.4</v>
+        <v>4663.98</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DE GOVERNO E O FORNECIMENTO DE ACESSO À REDE MetroMAO.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB A ESTA SEPROR</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2019NE00465</t>
+          <t>2019NE00466</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>6/2017</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>4663.98</v>
+        <v>1316.4</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB A ESTA SEPROR</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DE GOVERNO E O FORNECIMENTO DE ACESSO À REDE MetroMAO.</t>
         </is>
       </c>
     </row>
@@ -6030,12 +6030,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026NE0000002</t>
+          <t>2026NE0000003</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>4/2022</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>12655.88</v>
+        <v>5159.84</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -6053,19 +6053,19 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de Sistema de Protocolo via Web - (SPROWEB). TC: 0002/2024 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026NE0000001</t>
+          <t>2026NE0000004</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6074,7 +6074,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>10052.56</v>
+        <v>36075</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6083,19 +6083,19 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 04.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 06.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026NE0000004</t>
+          <t>2026NE0000001</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>36075</v>
+        <v>10052.56</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6113,19 +6113,19 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 06.</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 04.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026NE0000003</t>
+          <t>2026NE0000002</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6134,7 +6134,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>5159.84</v>
+        <v>12655.88</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de Sistema de Protocolo via Web - (SPROWEB). TC: 0002/2024 AD: 01.</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
@@ -6180,21 +6180,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2024NE0000743</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>6/2021</t>
-        </is>
-      </c>
+          <t>2024NE0000749</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
       <c r="C192" t="inlineStr">
         <is>
           <t>04/07/2024</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>4635.08</v>
+        <v>1784.34</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6203,28 +6199,24 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 03.</t>
+          <t>Para fins de regularização infomamos que a referida Nota de Empenho foi susbtituida pela NE 00077 de 19/02/2024.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2024NE0000751</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>4/2021</t>
-        </is>
-      </c>
+          <t>2024NE0000748</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
       <c r="C193" t="inlineStr">
         <is>
           <t>04/07/2024</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>18096.76</v>
+        <v>3476.3</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6233,24 +6225,28 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 05.</t>
+          <t>infomamos que a referida Nota de empenho foi susbtituida pela NE 00078 de 19/02/2024.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2024NE0000750</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr"/>
+          <t>2024NE0000739</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>4/2022</t>
+        </is>
+      </c>
       <c r="C194" t="inlineStr">
         <is>
           <t>04/07/2024</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>4374.14</v>
+        <v>2430.08</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6259,7 +6255,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Para fins de regularização infomamos que a referida Nota de Empenho foi susbtituida pela NE 00079 de 19/02/2024.</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
@@ -6296,21 +6292,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2024NE0000739</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>4/2022</t>
-        </is>
-      </c>
+          <t>2024NE0000750</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
       <c r="C196" t="inlineStr">
         <is>
           <t>04/07/2024</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>2430.08</v>
+        <v>4374.14</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6319,24 +6311,28 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>Para fins de regularização infomamos que a referida Nota de Empenho foi susbtituida pela NE 00079 de 19/02/2024.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2024NE0000748</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr"/>
+          <t>2024NE0000751</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>4/2021</t>
+        </is>
+      </c>
       <c r="C197" t="inlineStr">
         <is>
           <t>04/07/2024</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>3476.3</v>
+        <v>18096.76</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6345,24 +6341,28 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>infomamos que a referida Nota de empenho foi susbtituida pela NE 00078 de 19/02/2024.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 05.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2024NE0000749</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr"/>
+          <t>2024NE0000743</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>6/2021</t>
+        </is>
+      </c>
       <c r="C198" t="inlineStr">
         <is>
           <t>04/07/2024</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1784.34</v>
+        <v>4635.08</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6371,19 +6371,19 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Para fins de regularização infomamos que a referida Nota de Empenho foi susbtituida pela NE 00077 de 19/02/2024.</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2023NE0000645</t>
+          <t>2023NE0000647</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>3/2019</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1245.7</v>
+        <v>5822.3</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB). TC: 003/2019 AD: 03.</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2023NE0000647</t>
+          <t>2023NE0000645</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>4/2022</t>
+          <t>3/2019</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>5822.3</v>
+        <v>1245.7</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6461,19 +6461,19 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB). TC: 003/2019 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2021NE0000012</t>
+          <t>2021NE0000009</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>6/2017</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6482,7 +6482,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>11189.88</v>
+        <v>54288.64</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6491,19 +6491,19 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DE GOVERNO E O FORNECIMENTO DE ACESSO DE REDE METROMAO.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE REDE, COMPREENDENDO O ACESSO GERENCIADO A INTERNET COM VELOCIDADE DE 20Mpbs, ATRAVÉS DA REDE DE GOVERNO.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2021NE0000010</t>
+          <t>2021NE0000011</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>3/2019</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6512,7 +6512,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>7358.73</v>
+        <v>8913</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6521,19 +6521,19 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada nos serviços de Licença de uso de Sistema de informação, compreendendo a disponibilidade de Gestor de Conteúdo Web.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA A PRESTAÇÃO DE EXECUÇÃO DE SISTEMA PARA O PROCESSAMENTO DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2021NE0000011</t>
+          <t>2021NE0000010</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>3/2019</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6542,7 +6542,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>8913</v>
+        <v>7358.73</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6551,19 +6551,19 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA A PRESTAÇÃO DE EXECUÇÃO DE SISTEMA PARA O PROCESSAMENTO DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
+          <t>Contratação de empresa especializada nos serviços de Licença de uso de Sistema de informação, compreendendo a disponibilidade de Gestor de Conteúdo Web.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2021NE0000009</t>
+          <t>2021NE0000012</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>6/2017</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6572,7 +6572,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>54288.64</v>
+        <v>11189.88</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6581,14 +6581,14 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE REDE, COMPREENDENDO O ACESSO GERENCIADO A INTERNET COM VELOCIDADE DE 20Mpbs, ATRAVÉS DA REDE DE GOVERNO.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DE GOVERNO E O FORNECIMENTO DE ACESSO DE REDE METROMAO.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2016NE00064</t>
+          <t>2016NE00056</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>7797</v>
+        <v>10396</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2016NE00063</t>
+          <t>2016NE00058</t>
         </is>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE N° 59 PARA AJUSTES</t>
+          <t>ANULAÇÃO DA NE N° 56 PARA AJUSTES NA DESCRIÇÃO DA NE.</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2016NE00058</t>
+          <t>2016NE00063</t>
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -6693,14 +6693,14 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE N° 56 PARA AJUSTES NA DESCRIÇÃO DA NE.</t>
+          <t>ANULAÇÃO DA NE N° 59 PARA AJUSTES</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2016NE00056</t>
+          <t>2016NE00064</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6714,7 +6714,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>10396</v>
+        <v>7797</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -6730,12 +6730,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2022NE0002183</t>
+          <t>2022NE0002182</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>3/2019</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6744,7 +6744,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>2232.91</v>
+        <v>1167.84</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -6753,19 +6753,19 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web)</t>
+          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2022NE0002181</t>
+          <t>2022NE0002184</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>11977.5</v>
+        <v>2911.15</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -6783,19 +6783,19 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial.</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2022NE0002184</t>
+          <t>2022NE0002181</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>4/2022</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6804,7 +6804,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>2911.15</v>
+        <v>11977.5</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -6813,19 +6813,19 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2022NE0002182</t>
+          <t>2022NE0002183</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>3/2019</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6834,7 +6834,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1167.84</v>
+        <v>2232.91</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -6843,14 +6843,14 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB).</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web)</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2016NE00852</t>
+          <t>2016NE00854</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -6869,28 +6869,24 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO VALOR TOTAL DA NE N° 255/2016, PARA UTILIZAÇÃO DO RECURSO PARA PAGAMENTO DE DESPESAS REFERENTE AO TCT N° 08/2016-SEPROR.</t>
+          <t>REFORÇO DA NE N° 516/2016, PARA PAGAMENTO DE DESPESAS REFERENTE AO TCT N° 08/2016-SEPROR.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2016NE00854</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>8/2016</t>
-        </is>
-      </c>
+          <t>2016NE00852</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
       <c r="C216" t="inlineStr">
         <is>
           <t>03/10/2016</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -6899,7 +6895,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE N° 516/2016, PARA PAGAMENTO DE DESPESAS REFERENTE AO TCT N° 08/2016-SEPROR.</t>
+          <t>ANULAÇÃO DO VALOR TOTAL DA NE N° 255/2016, PARA UTILIZAÇÃO DO RECURSO PARA PAGAMENTO DE DESPESAS REFERENTE AO TCT N° 08/2016-SEPROR.</t>
         </is>
       </c>
     </row>
@@ -6958,17 +6954,21 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2016NE00852</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr"/>
+          <t>2016NE00854</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>8/2016</t>
+        </is>
+      </c>
       <c r="C219" t="inlineStr">
         <is>
           <t>03/10/2016</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -6977,14 +6977,14 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO VALOR TOTAL DA NE N° 255/2016, PARA UTILIZAÇÃO DO RECURSO PARA PAGAMENTO DE DESPESAS REFERENTE AO TCT N° 08/2016-SEPROR.</t>
+          <t>REFORÇO DA NE N° 516/2016, PARA PAGAMENTO DE DESPESAS REFERENTE AO TCT N° 08/2016-SEPROR.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2016NE00854</t>
+          <t>2016NE00852</t>
         </is>
       </c>
       <c r="B220" t="inlineStr"/>
@@ -6994,7 +6994,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -7003,19 +7003,19 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE N° 516/2016, PARA PAGAMENTO DE DESPESAS REFERENTE AO TCT N° 08/2016-SEPROR.</t>
+          <t>ANULAÇÃO DO VALOR TOTAL DA NE N° 255/2016, PARA UTILIZAÇÃO DO RECURSO PARA PAGAMENTO DE DESPESAS REFERENTE AO TCT N° 08/2016-SEPROR.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2021NE0000667</t>
+          <t>2021NE0000668</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7024,7 +7024,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>7580.76</v>
+        <v>40678</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -7033,19 +7033,19 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de Licença de Informação - GERWEB (Gestor de Conteúdo Web).</t>
+          <t>Contratação de empresa especializada no serviço de link de acesso a rede mundial (Internet e dados).</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2021NE0000669</t>
+          <t>2021NE0000647</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>3/2019</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>8629.360000000001</v>
+        <v>7036.24</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7063,19 +7063,19 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de rede, compreendendo o acesso a rede de governo e o fornecimento de acesso de rede Metromao.</t>
+          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2021NE0000647</t>
+          <t>2021NE0000669</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>3/2019</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>7036.24</v>
+        <v>8629.360000000001</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -7093,19 +7093,19 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB).</t>
+          <t>Contratação de empresa especializada em serviços de rede, compreendendo o acesso a rede de governo e o fornecimento de acesso de rede Metromao.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2021NE0000668</t>
+          <t>2021NE0000667</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>40678</v>
+        <v>7580.76</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de link de acesso a rede mundial (Internet e dados).</t>
+          <t>Contratação de empresa especializada no serviço de Licença de Informação - GERWEB (Gestor de Conteúdo Web).</t>
         </is>
       </c>
     </row>
@@ -7160,12 +7160,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2022NE0000794</t>
+          <t>2022NE0000790</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>3/2019</t>
+          <t>6/2017</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7174,7 +7174,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1876.33</v>
+        <v>6040.55</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -7183,19 +7183,19 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB).</t>
+          <t>Contratação de empresa especializada em serviços de rede, compreendendo o acesso a rede de governo e o fornecimento de acesso de rede Metromao.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2022NE0000790</t>
+          <t>2022NE0000794</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>6/2017</t>
+          <t>3/2019</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>6040.55</v>
+        <v>1876.33</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de rede, compreendendo o acesso a rede de governo e o fornecimento de acesso de rede Metromao.</t>
+          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB).</t>
         </is>
       </c>
     </row>
@@ -7276,12 +7276,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2022NE0000037</t>
+          <t>2022NE0000034</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>6/2017</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7290,7 +7290,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>7580.76</v>
+        <v>8629.360000000001</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de Licença de Informação - GERWEB (Gestor de Conteúdo Web).</t>
+          <t>Contratação de empresa especializada em serviços de rede, compreendendo o acesso a rede de governo e o fornecimento de acesso de rede Metromao.</t>
         </is>
       </c>
     </row>
@@ -7336,12 +7336,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2022NE0000034</t>
+          <t>2022NE0000037</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>6/2017</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>8629.360000000001</v>
+        <v>7580.76</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de rede, compreendendo o acesso a rede de governo e o fornecimento de acesso de rede Metromao.</t>
+          <t>Contratação de empresa especializada no serviço de Licença de Informação - GERWEB (Gestor de Conteúdo Web).</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7396,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2025NE0000475</t>
+          <t>2025NE00475</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -7410,7 +7410,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>3691.3</v>
+        <v>32191.3</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -7419,14 +7419,14 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>Cobertura Contratual</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2025NE00475</t>
+          <t>2025NE0000475</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>32191.3</v>
+        <v>3691.3</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Cobertura Contratual</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
@@ -7486,10 +7486,14 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2017NE00296</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr"/>
+          <t>2017NE00297</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>12/2016</t>
+        </is>
+      </c>
       <c r="C237" t="inlineStr">
         <is>
           <t>02/05/2017</t>
@@ -7505,14 +7509,14 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE N° 291/17 PARA AJUSTES NO EMPENHO</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE CESSÃO DE LICENÇA DE USO DO SISTEMA SGTI - CHAMADAS, FERRAMENTA PARA DAR SUPORTE À GESTÃO DE ATENDIMENTOS DE DEMANDAS EXTERNAS E INTERNAS.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2017NE00291</t>
+          <t>2017NE00288</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -7568,7 +7572,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2017NE00288</t>
+          <t>2017NE00291</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -7598,14 +7602,10 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2017NE00297</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>12/2016</t>
-        </is>
-      </c>
+          <t>2017NE00296</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr"/>
       <c r="C241" t="inlineStr">
         <is>
           <t>02/05/2017</t>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE CESSÃO DE LICENÇA DE USO DO SISTEMA SGTI - CHAMADAS, FERRAMENTA PARA DAR SUPORTE À GESTÃO DE ATENDIMENTOS DE DEMANDAS EXTERNAS E INTERNAS.</t>
+          <t>ANULAÇÃO DA NE N° 291/17 PARA AJUSTES NO EMPENHO</t>
         </is>
       </c>
     </row>
@@ -7688,12 +7688,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2025NE0000005</t>
+          <t>2025NE0000007</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7702,7 +7702,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>18096.76</v>
+        <v>2379.12</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -7711,19 +7711,19 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 05.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de Sistema de Protocolo via Web - (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2025NE0000002</t>
+          <t>2025NE0000008</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7732,7 +7732,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>4635.08</v>
+        <v>5832.2</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -7741,19 +7741,19 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 03.</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2025NE0000008</t>
+          <t>2025NE0000002</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>4/2022</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>5832.2</v>
+        <v>4635.08</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -7771,19 +7771,19 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2025NE0000007</t>
+          <t>2025NE0000005</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2/2024</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -7792,7 +7792,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>2379.12</v>
+        <v>18096.76</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -7801,19 +7801,19 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de Sistema de Protocolo via Web - (SPROWEB).</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial, conforme PARECER N.º 081/2023. TC: 0004/2021 AD: 05.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2024NE0000044</t>
+          <t>2024NE0000042</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>3/2019</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -7822,7 +7822,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1784.34</v>
+        <v>3476.3</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB). TC: 0003/2019 AD: 05.</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 03.</t>
         </is>
       </c>
     </row>
@@ -7868,12 +7868,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2024NE0000042</t>
+          <t>2024NE0000044</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>3/2019</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7882,7 +7882,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>3476.3</v>
+        <v>1784.34</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -7891,19 +7891,19 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web). TC: 0006/2021 AD: 03.</t>
+          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB). TC: 0003/2019 AD: 05.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2023NE0000008</t>
+          <t>2023NE0000009</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>4/2022</t>
+          <t>6/2021</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -7912,7 +7912,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>11644.6</v>
+        <v>8931.639999999999</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -7921,19 +7921,19 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
+          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web)</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2023NE0000005</t>
+          <t>2023NE0000007</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>3/2019</t>
+          <t>4/2021</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>4671.36</v>
+        <v>44316.75</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -7951,19 +7951,19 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB).</t>
+          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2023NE0000007</t>
+          <t>2023NE0000005</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>4/2021</t>
+          <t>3/2019</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -7972,7 +7972,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>44316.75</v>
+        <v>4671.36</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -7981,19 +7981,19 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de acesso gerenciado a Rede Mundial.</t>
+          <t>Contratação de empresa especializada para a prestação de execução de sistema para o processamento de protocolo plataforma web (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2023NE0000009</t>
+          <t>2023NE0000008</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>6/2021</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -8002,7 +8002,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>8931.639999999999</v>
+        <v>11644.6</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -8011,19 +8011,19 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada no serviço de licença de informação - GERWEB (Gestor de Conteúdo Web)</t>
+          <t>Contratação de empresa especializada no fornecimento de serviços de manutenção e acesso da Rede Metropolitana Manaus - REPAM/METROMAO. Funcionando como link principal no acesso aos serviços prestados.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2020NE00004</t>
+          <t>2020NE00002</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>3/2019</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>7358.68</v>
+        <v>8912.559999999999</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -8041,24 +8041,28 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB A ESTA SEPROR</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA, PARA PROCESSAMENTO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB(SPROWeb).</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2020NE00017</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr"/>
+          <t>2020NE00003</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>8/2016</t>
+        </is>
+      </c>
       <c r="C256" t="inlineStr">
         <is>
           <t>02/01/2020</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>8912.559999999999</v>
+        <v>50590.16</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -8067,19 +8071,19 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DA NE N° 02 DE 02/01/2020, DEVIDO VALORES INCORRETOS NO INCORRETOS NO DETACONTRATO.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE REDE, COMPREENDENDO O ACESSO GERENCIADO A INTERNET COM VELOCIDADE DE 20Mbps, ATRAVÉS DA REDE DE GOVERNO.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2020NE00020</t>
+          <t>2020NE00001</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>3/2019</t>
+          <t>6/2017</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -8088,7 +8092,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>8912.440000000001</v>
+        <v>11244.73</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -8097,19 +8101,19 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA, PARA PROCESSAMENTO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB(SPROWeb).</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DE GOVERNO E O FORNECIMENTO DE ACESSO A REDE METROMAO</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2020NE00001</t>
+          <t>2020NE00020</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>6/2017</t>
+          <t>3/2019</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -8118,7 +8122,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>11244.73</v>
+        <v>8912.440000000001</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -8127,28 +8131,24 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DE GOVERNO E O FORNECIMENTO DE ACESSO A REDE METROMAO</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA, PARA PROCESSAMENTO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB(SPROWeb).</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2020NE00003</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>8/2016</t>
-        </is>
-      </c>
+          <t>2020NE00017</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr"/>
       <c r="C259" t="inlineStr">
         <is>
           <t>02/01/2020</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>50590.16</v>
+        <v>8912.559999999999</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -8157,19 +8157,19 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE REDE, COMPREENDENDO O ACESSO GERENCIADO A INTERNET COM VELOCIDADE DE 20Mbps, ATRAVÉS DA REDE DE GOVERNO.</t>
+          <t>CANCELAMENTO DA NE N° 02 DE 02/01/2020, DEVIDO VALORES INCORRETOS NO INCORRETOS NO DETACONTRATO.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2020NE00002</t>
+          <t>2020NE00004</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>3/2019</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>8912.559999999999</v>
+        <v>7358.68</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -8187,19 +8187,19 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA, PARA PROCESSAMENTO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB(SPROWeb).</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB A ESTA SEPROR</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2019NE00005</t>
+          <t>2019NE00002</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>47040</v>
+        <v>4663.98</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE REDE, COMPREENDENDO O ACESSO GERENCIADO À INTERNET COM VELOCIDADE DE 20Mbps, ATRAVÉS DA REDE DE GOVERNO.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB A ESTA SEPROR.</t>
         </is>
       </c>
     </row>
@@ -8254,12 +8254,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2019NE00002</t>
+          <t>2019NE00005</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>4663.98</v>
+        <v>47040</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -8277,19 +8277,19 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB A ESTA SEPROR.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE REDE, COMPREENDENDO O ACESSO GERENCIADO À INTERNET COM VELOCIDADE DE 20Mbps, ATRAVÉS DA REDE DE GOVERNO.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2018NE00055</t>
+          <t>2018NE00063</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>6/2017</t>
+          <t>12/2016</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8298,7 +8298,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>11496.03</v>
+        <v>18421.44</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -8307,19 +8307,19 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA CONSTRUÇÃO DE CIRCUITO OPTICA PARA INSTALAR LINK DE ACESSO A REDE MUNDIAL E FORNECIMENTO DE ACESSO A REDE METROMAO.</t>
+          <t>PRORROGAÇÃO DO PRAZO DE VIGÊNCIA POR MAIS 12 MESES E REAJUSTE DE 3,36% NO SERVIÇO DE CESSÃO DE LICENÇA DE USO DO SISTEMA SGTI- CHAMADAS, FERRAMENTA PARA DAR SUPORTE À GESTÃO DE DEMANDAS EXTERNAS E INT</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2018NE00054</t>
+          <t>2018NE00064</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>12/2017</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>7773.3</v>
+        <v>37224.99</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>PRORROGAÇÃO DE PRAZO DO CONTRATO PRIMITIVO POR MAIS 12 MESES, COM REAJUSTE CONTRATUAL DE 5,38%, NA LICENÇA DE USO DO SISTEMA DE INFORMAÇÃO- GERWEB.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA A PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO.</t>
         </is>
       </c>
     </row>
@@ -8374,12 +8374,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2018NE00064</t>
+          <t>2018NE00054</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>12/2017</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -8388,7 +8388,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>37224.99</v>
+        <v>7773.3</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -8397,19 +8397,19 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA A PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO.</t>
+          <t>PRORROGAÇÃO DE PRAZO DO CONTRATO PRIMITIVO POR MAIS 12 MESES, COM REAJUSTE CONTRATUAL DE 5,38%, NA LICENÇA DE USO DO SISTEMA DE INFORMAÇÃO- GERWEB.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2018NE00063</t>
+          <t>2018NE00055</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>12/2016</t>
+          <t>6/2017</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8418,7 +8418,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>18421.44</v>
+        <v>11496.03</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -8427,19 +8427,19 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>PRORROGAÇÃO DO PRAZO DE VIGÊNCIA POR MAIS 12 MESES E REAJUSTE DE 3,36% NO SERVIÇO DE CESSÃO DE LICENÇA DE USO DO SISTEMA SGTI- CHAMADAS, FERRAMENTA PARA DAR SUPORTE À GESTÃO DE DEMANDAS EXTERNAS E INT</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA CONSTRUÇÃO DE CIRCUITO OPTICA PARA INSTALAR LINK DE ACESSO A REDE MUNDIAL E FORNECIMENTO DE ACESSO A REDE METROMAO.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2017NE00024</t>
+          <t>2017NE00013</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>2/2012</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>36000</v>
+        <v>7797</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -8457,19 +8457,19 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE CONEXÃO DE INTERNET VIA FIBRA ÓPTICA.</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE CESSÃO, DIREITO DE USO DE PROGRAMAS PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO SPROWEB.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2017NE00014</t>
+          <t>2017NE00022</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>12/2016</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>5901.16</v>
+        <v>11881.72</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -8487,19 +8487,19 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE DESENVOLVIMENTO DE WEBSITE.</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE CESSÃO DE LICENÇA DE USO DO SISTEMA SGTI - CHAMADAS, FERRAMENTA PARA DAR SUPORTE À GESTÃO DE ATENDIMENTOS DE DEMANDAS EXTERNAS E INTERNAS.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2017NE00022</t>
+          <t>2017NE00014</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>12/2016</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -8508,7 +8508,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>11881.72</v>
+        <v>5901.16</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -8517,19 +8517,19 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE CESSÃO DE LICENÇA DE USO DO SISTEMA SGTI - CHAMADAS, FERRAMENTA PARA DAR SUPORTE À GESTÃO DE ATENDIMENTOS DE DEMANDAS EXTERNAS E INTERNAS.</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE DESENVOLVIMENTO DE WEBSITE.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2017NE00013</t>
+          <t>2017NE00024</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2/2012</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -8538,7 +8538,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>7797</v>
+        <v>36000</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE CESSÃO, DIREITO DE USO DE PROGRAMAS PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO SPROWEB.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE CONEXÃO DE INTERNET VIA FIBRA ÓPTICA.</t>
         </is>
       </c>
     </row>
@@ -8584,12 +8584,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2017NE01071</t>
+          <t>2017NE01074</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>12/2016</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -8598,7 +8598,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1554.66</v>
+        <v>3070.24</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -8607,19 +8607,19 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>PRORROGAÇÃO DE PRAZO DO CONTRATO PRIMITIVO POR MAIS 12 MESES, COM REAJUSTE CONTRATUAL DE 5,38%, NA LICENÇA DE USO DO SISTEMA DE INFORMAÇÃO- GERWEB.</t>
+          <t>PRORROGAÇÃO DO PRAZO DE VIGÊNCIA POR MAIS 12 MESES E REAJUSTE DE 3,36% NO SERVIÇO DE CESSÃO DE LICENÇA DE USO DO SISTEMA SGTI- CHAMADAS, FERRAMENTA PARA DAR SUPORTE À GESTÃO DE DEMANDAS EXTERNAS E INT</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2017NE01078</t>
+          <t>2017NE01073</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>12/2017</t>
+          <t>6/2017</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>3384.09</v>
+        <v>1642.29</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA A PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO.</t>
+          <t>Contratação de empresa especializada na construção de circuito de fibra óptica para instalar link de acesso a rede mundial e fornecimento de acesso a rede METROMAO.</t>
         </is>
       </c>
     </row>
@@ -8674,12 +8674,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2017NE01073</t>
+          <t>2017NE01078</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>6/2017</t>
+          <t>12/2017</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -8688,7 +8688,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>1642.29</v>
+        <v>3384.09</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -8697,19 +8697,19 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na construção de circuito de fibra óptica para instalar link de acesso a rede mundial e fornecimento de acesso a rede METROMAO.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA A PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2017NE01074</t>
+          <t>2017NE01071</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>12/2016</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -8718,7 +8718,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>3070.24</v>
+        <v>1554.66</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -8727,19 +8727,19 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>PRORROGAÇÃO DO PRAZO DE VIGÊNCIA POR MAIS 12 MESES E REAJUSTE DE 3,36% NO SERVIÇO DE CESSÃO DE LICENÇA DE USO DO SISTEMA SGTI- CHAMADAS, FERRAMENTA PARA DAR SUPORTE À GESTÃO DE DEMANDAS EXTERNAS E INT</t>
+          <t>PRORROGAÇÃO DE PRAZO DO CONTRATO PRIMITIVO POR MAIS 12 MESES, COM REAJUSTE CONTRATUAL DE 5,38%, NA LICENÇA DE USO DO SISTEMA DE INFORMAÇÃO- GERWEB.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2016NE00911</t>
+          <t>2016NE00912</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2/2012</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>7797</v>
+        <v>18000</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE CESSÃO, DIREITO DE USO DE PROGRAMAS PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO SPROWEB.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE CONEXÃO DE INTERNET VIA FIBRA ÓPTICA.</t>
         </is>
       </c>
     </row>
@@ -8794,12 +8794,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2016NE00912</t>
+          <t>2016NE00911</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>2/2012</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>18000</v>
+        <v>7797</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -8817,19 +8817,19 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE CONEXÃO DE INTERNET VIA FIBRA ÓPTICA.</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE CESSÃO, DIREITO DE USO DE PROGRAMAS PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO SPROWEB.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2019NE00750</t>
+          <t>2019NE00741</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>3/2019</t>
+          <t>6/2017</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>5277.18</v>
+        <v>4936.71</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -8847,19 +8847,19 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA, PARA PROCESSAMENTO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB(SPROWeb).</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DE GOVERNO E O FORNECIMENTO DE ACESSO A REDE METROMAO</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2019NE00742</t>
+          <t>2019NE00747</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -8868,7 +8868,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>4663.98</v>
+        <v>56913.93</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -8877,19 +8877,19 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB A ESTA SEPROR</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE REDE, COMPREENDENDO O ACESSO GERENCIADO A INTERNET COM VELOCIDADE DE 20Mbps, ATRAVÉS DA REDE DE GOVERNO.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2019NE00747</t>
+          <t>2019NE00742</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -8898,7 +8898,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>56913.93</v>
+        <v>4663.98</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -8907,19 +8907,19 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE REDE, COMPREENDENDO O ACESSO GERENCIADO A INTERNET COM VELOCIDADE DE 20Mbps, ATRAVÉS DA REDE DE GOVERNO.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB A ESTA SEPROR</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2019NE00741</t>
+          <t>2019NE00750</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>6/2017</t>
+          <t>3/2019</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>4936.71</v>
+        <v>5277.18</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -8937,24 +8937,28 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DE GOVERNO E O FORNECIMENTO DE ACESSO A REDE METROMAO</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA, PARA PROCESSAMENTO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB(SPROWeb).</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2017NE00790</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr"/>
+          <t>2017NE00789</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>11/2016</t>
+        </is>
+      </c>
       <c r="C286" t="inlineStr">
         <is>
           <t>01/09/2017</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>6140.48</v>
+        <v>3109.32</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -8963,14 +8967,14 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>PRORROGAÇÃO DO PRAZO DE VIGÊNCIA POR MAIS 12 MESES E REAJUSTE DE 3,36% NO SERVIÇO DE CESSÃO DE LICENÇA DE USO DO SISTEMA SGTI- CHAMADAS, FERRAMENTA PARA DAR SUPORTE À GESTÃO DE DEMANDAS EXTERNAS E INT</t>
+          <t>PRORROGAÇÃO DE PRAZO DO CONTRATO PRIMITIVO POR MAIS 12 MESES, COM REAJUSTE CONTRATUAL DE 5,38%, NA LICENÇA DE USO DO SISTEMA DE INFORMAÇÃO- GERWEB.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2017NE00788</t>
+          <t>2017NE00791</t>
         </is>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -8980,7 +8984,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>35280</v>
+        <v>3284.58</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -8989,14 +8993,14 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Prorrogação por mais 12 meses e supressão de 2% do contrato inicial.</t>
+          <t>Contratação de empresa especializada na construção de circuito de fibra óptica para instalar link de acesso a rede mundial e fornecimento de acesso a rede METROMAO.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2017NE00791</t>
+          <t>2017NE00788</t>
         </is>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -9006,7 +9010,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>3284.58</v>
+        <v>35280</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -9015,28 +9019,24 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na construção de circuito de fibra óptica para instalar link de acesso a rede mundial e fornecimento de acesso a rede METROMAO.</t>
+          <t>Prorrogação por mais 12 meses e supressão de 2% do contrato inicial.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2017NE00789</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>11/2016</t>
-        </is>
-      </c>
+          <t>2017NE00790</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr"/>
       <c r="C289" t="inlineStr">
         <is>
           <t>01/09/2017</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>3109.32</v>
+        <v>6140.48</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -9045,19 +9045,19 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>PRORROGAÇÃO DE PRAZO DO CONTRATO PRIMITIVO POR MAIS 12 MESES, COM REAJUSTE CONTRATUAL DE 5,38%, NA LICENÇA DE USO DO SISTEMA DE INFORMAÇÃO- GERWEB.</t>
+          <t>PRORROGAÇÃO DO PRAZO DE VIGÊNCIA POR MAIS 12 MESES E REAJUSTE DE 3,36% NO SERVIÇO DE CESSÃO DE LICENÇA DE USO DO SISTEMA SGTI- CHAMADAS, FERRAMENTA PARA DAR SUPORTE À GESTÃO DE DEMANDAS EXTERNAS E INT</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2016NE00516</t>
+          <t>2016NE00561</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9066,7 +9066,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>54000</v>
+        <v>4425.87</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -9075,19 +9075,19 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE CONEXÃO DE INTERNET VIA FIBRA ÓPTICA.</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE DESENVOLVIMENTO DE WEBSITE.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2016NE00517</t>
+          <t>2016NE00518</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2/2012</t>
+          <t>12/2016</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -9096,7 +9096,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>7797</v>
+        <v>11881.72</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -9105,19 +9105,19 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE CESSÃO, DIREITO DE USO DE PROGRAMAS PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO SPROWEB.</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE CESSÃO DE LICENÇA DE USO DO SISTEMA SGTI - CHAMADAS, FERRAMENTA PARA DAR SUPORTE À GESTÃO DE ATENDIMENTOS DE DEMANDAS EXTERNAS E INTERNAS.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2016NE00518</t>
+          <t>2016NE00517</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>12/2016</t>
+          <t>2/2012</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -9126,7 +9126,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>11881.72</v>
+        <v>7797</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -9135,19 +9135,19 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE CESSÃO DE LICENÇA DE USO DO SISTEMA SGTI - CHAMADAS, FERRAMENTA PARA DAR SUPORTE À GESTÃO DE ATENDIMENTOS DE DEMANDAS EXTERNAS E INTERNAS.</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE CESSÃO, DIREITO DE USO DE PROGRAMAS PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO SPROWEB.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2016NE00561</t>
+          <t>2016NE00516</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -9156,7 +9156,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>4425.87</v>
+        <v>54000</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -9165,19 +9165,19 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE DESENVOLVIMENTO DE WEBSITE.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE CONEXÃO DE INTERNET VIA FIBRA ÓPTICA.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2019NE00148</t>
+          <t>2019NE00142</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>11/2016</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9186,7 +9186,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>56913.93</v>
+        <v>2694.7</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -9195,28 +9195,24 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE REDE, COMPREENDENDO O ACESSO GERENCIADO A INTERNET COM VELOCIDADE DE 20Mbps, ATRAVÉS DA REDE DE GOVERNO.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB A ESSA SEPROR.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2019NE00149</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>6/2017</t>
-        </is>
-      </c>
+          <t>2019NE00152</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr"/>
       <c r="C295" t="inlineStr">
         <is>
           <t>01/04/2019</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>4936.71</v>
+        <v>2694.7</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -9225,7 +9221,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DE GOVERNO E O FORNECIMENTO DE ACESSO À REDE MetroMAO.</t>
+          <t>CANCELAMENTO DEVIDO DESCRIÇÃO INCORRETA</t>
         </is>
       </c>
     </row>
@@ -9262,17 +9258,21 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2019NE00152</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr"/>
+          <t>2019NE00149</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>6/2017</t>
+        </is>
+      </c>
       <c r="C297" t="inlineStr">
         <is>
           <t>01/04/2019</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>2694.7</v>
+        <v>4936.71</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -9281,19 +9281,19 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DEVIDO DESCRIÇÃO INCORRETA</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE REDE, COMPREENDENDO O ACESSO A REDE DE GOVERNO E O FORNECIMENTO DE ACESSO À REDE MetroMAO.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2019NE00142</t>
+          <t>2019NE00148</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>11/2016</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9302,7 +9302,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>2694.7</v>
+        <v>56913.93</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB A ESSA SEPROR.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE REDE, COMPREENDENDO O ACESSO GERENCIADO A INTERNET COM VELOCIDADE DE 20Mbps, ATRAVÉS DA REDE DE GOVERNO.</t>
         </is>
       </c>
     </row>

--- a/DOSSIES_MULTIFORMATO/SEPROR/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SEPROR/dossie.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2028-08-31</t>
         </is>
       </c>
     </row>
